--- a/data/trans_dic/P1422-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1422-Edad-trans_dic.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,43</t>
+          <t>0,55; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,89</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,28</t>
+          <t>0,22; 1,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,58</t>
+          <t>0,06; 0,56</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,67</t>
+          <t>0,17; 1,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,66</t>
+          <t>0,3; 1,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,4</t>
+          <t>0,39; 1,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,18</t>
+          <t>0,34; 2,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,02</t>
+          <t>0,2; 1,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,47</t>
+          <t>0,4; 1,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,09</t>
+          <t>0,23; 1,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,04</t>
+          <t>0,37; 1,21</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,95</t>
+          <t>1,48; 3,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,06</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,28</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,28</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,68</t>
+          <t>0,91; 2,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,11</t>
+          <t>0,11; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,12</t>
+          <t>0,12; 1,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,84</t>
+          <t>1,41; 2,89</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,09</t>
+          <t>0,64; 3,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,26</t>
+          <t>0,82; 4,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,13</t>
+          <t>0,92; 3,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,78</t>
+          <t>0,85; 3,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,95</t>
+          <t>0,75; 3,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,23</t>
+          <t>0,94; 2,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,03</t>
+          <t>0,93; 3,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,4</t>
+          <t>0,99; 3,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,25</t>
+          <t>1,21; 2,63</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,88</t>
+          <t>2,54; 9,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,07</t>
+          <t>0,91; 3,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,04</t>
+          <t>2,88; 6,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,39</t>
+          <t>1,47; 5,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,79</t>
+          <t>1,11; 4,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,98</t>
+          <t>1,82; 4,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,15</t>
+          <t>2,49; 5,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,84</t>
+          <t>1,19; 3,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,73</t>
+          <t>2,57; 4,76</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,42</t>
+          <t>0,65; 1,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,94</t>
+          <t>0,41; 0,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,57</t>
+          <t>0,96; 1,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,06</t>
+          <t>0,46; 1,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,9</t>
+          <t>0,35; 0,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,22</t>
+          <t>0,81; 1,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,09</t>
+          <t>0,64; 1,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,84</t>
+          <t>0,43; 0,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,31</t>
+          <t>0,94; 1,36</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1336</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6036</t>
+          <t>0; 7043</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6485</t>
+          <t>0; 6626</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>947</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2312</t>
         </is>
       </c>
     </row>
@@ -1913,17 +1913,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5187</t>
+          <t>0; 5153</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4921</t>
+          <t>0; 4901</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5351</t>
+          <t>0; 7436</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5349</t>
+          <t>0; 5533</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5179</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5515</t>
+          <t>0; 4883</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 7640</t>
+          <t>0; 7336</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2925</t>
         </is>
       </c>
     </row>
@@ -2076,17 +2076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3748; 16567</t>
+          <t>3764; 16217</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5593</t>
+          <t>0; 5672</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4325</t>
+          <t>0; 5471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>161; 4810</t>
+          <t>0; 5982</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3724; 17862</t>
+          <t>3013; 15952</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 6490</t>
+          <t>0; 6408</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>595; 6272</t>
+          <t>739; 6899</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>10132</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1025; 10243</t>
+          <t>1045; 9932</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1882; 10728</t>
+          <t>1935; 12334</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1421; 12411</t>
+          <t>2745; 12891</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2945; 13367</t>
+          <t>2112; 12315</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7038</t>
+          <t>0; 8429</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1360; 7299</t>
+          <t>1508; 8009</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5094; 18103</t>
+          <t>4913; 18248</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2987; 14077</t>
+          <t>3035; 14399</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4234; 16654</t>
+          <t>5273; 17346</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>24834</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6972</t>
+          <t>0; 7057</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7931</t>
+          <t>0; 7978</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8242; 22146</t>
+          <t>8988; 24108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5726</t>
+          <t>0; 4747</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6379</t>
+          <t>0; 6359</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4835; 14573</t>
+          <t>5518; 15843</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>940; 9746</t>
+          <t>933; 7917</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1131; 10879</t>
+          <t>1131; 10091</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14610; 31392</t>
+          <t>17134; 35146</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14923</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2030; 12655</t>
+          <t>1976; 11692</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2808; 14249</t>
+          <t>2746; 14683</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3429; 11449</t>
+          <t>3729; 12222</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2988; 13364</t>
+          <t>3017; 12493</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2774; 14920</t>
+          <t>2817; 14780</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2476; 13560</t>
+          <t>4138; 13010</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6078; 20132</t>
+          <t>6197; 20805</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7726; 24245</t>
+          <t>7055; 23328</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6534; 21870</t>
+          <t>10222; 22181</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25205</t>
+          <t>27037</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6465; 24694</t>
+          <t>6335; 23636</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1693; 10462</t>
+          <t>2351; 9785</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8926; 19915</t>
+          <t>8921; 21336</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6220; 20981</t>
+          <t>5728; 20521</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4469; 19187</t>
+          <t>4449; 19662</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7804; 16962</t>
+          <t>8421; 19135</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16725; 39293</t>
+          <t>15916; 38134</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7912; 25222</t>
+          <t>7845; 23959</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18510; 33506</t>
+          <t>19912; 36873</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>83499</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23652; 48721</t>
+          <t>22359; 48363</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13945; 32006</t>
+          <t>13997; 32775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30356; 54428</t>
+          <t>33968; 57277</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16597; 37842</t>
+          <t>16530; 37599</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12769; 31761</t>
+          <t>12309; 33118</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25426; 44643</t>
+          <t>30323; 50455</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44325; 76054</t>
+          <t>44556; 75941</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>31121; 58608</t>
+          <t>29670; 58871</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60011; 93365</t>
+          <t>68425; 98810</t>
         </is>
       </c>
     </row>
